--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2649,49 +2649,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133325609</v>
+        <v>137291050</v>
       </c>
       <c r="B17" t="n">
-        <v>58136</v>
+        <v>57213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2730,22 +2726,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2768,71 +2764,77 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Tjäderinventering Västmanland</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133325609</t>
+          <t>https://artportalen.se/Sighting/137291050</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127128691</v>
+        <v>133325609</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åkerbo, Vstm</t>
+          <t>Hjortronmossen, Kolsva, Köping, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555751</v>
+        <v>556019</v>
       </c>
       <c r="R18" t="n">
-        <v>6615525</v>
+        <v>6615764</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2856,22 +2858,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2882,25 +2884,151 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Nyberg</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Nyberg</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133325609</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127128691</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Åkerbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>555751</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6615525</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127128691</t>
         </is>
@@ -2925,6 +3053,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -2652,7 +2652,7 @@
         <v>137291050</v>
       </c>
       <c r="B17" t="n">
-        <v>57213</v>
+        <v>57223</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -2652,7 +2652,7 @@
         <v>137291050</v>
       </c>
       <c r="B17" t="n">
-        <v>57223</v>
+        <v>57224</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -2652,7 +2652,7 @@
         <v>137291050</v>
       </c>
       <c r="B17" t="n">
-        <v>57224</v>
+        <v>57227</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
